--- a/pages/shp/uploads/BC 2.7 20-05-2026 - 20-05-2026.xlsx
+++ b/pages/shp/uploads/BC 2.7 20-05-2026 - 20-05-2026.xlsx
@@ -1,34 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EXIM\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA28B19-1010-4FE2-9E4A-B7CF6AF48D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="HEADER" r:id="rId3" sheetId="1"/>
-    <sheet name="ENTITAS" r:id="rId4" sheetId="2"/>
-    <sheet name="DOKUMEN" r:id="rId5" sheetId="3"/>
-    <sheet name="PENGANGKUT" r:id="rId6" sheetId="4"/>
-    <sheet name="KEMASAN" r:id="rId7" sheetId="5"/>
-    <sheet name="KONTAINER" r:id="rId8" sheetId="6"/>
-    <sheet name="KOMPONENBIAYA" r:id="rId9" sheetId="7"/>
-    <sheet name="BARANG" r:id="rId10" sheetId="8"/>
-    <sheet name="BARANGTARIF" r:id="rId11" sheetId="9"/>
-    <sheet name="BARANGDOKUMEN" r:id="rId12" sheetId="10"/>
-    <sheet name="BARANGENTITAS" r:id="rId13" sheetId="11"/>
-    <sheet name="BARANGSPEKKHUSUS" r:id="rId14" sheetId="12"/>
-    <sheet name="BARANGVD" r:id="rId15" sheetId="13"/>
-    <sheet name="BAHANBAKU" r:id="rId16" sheetId="14"/>
-    <sheet name="BAHANBAKUTARIF" r:id="rId17" sheetId="15"/>
-    <sheet name="BAHANBAKUDOKUMEN" r:id="rId18" sheetId="16"/>
-    <sheet name="PUNGUTAN" r:id="rId19" sheetId="17"/>
-    <sheet name="JAMINAN" r:id="rId20" sheetId="18"/>
-    <sheet name="BANKDEVISA" r:id="rId21" sheetId="19"/>
-    <sheet name="VERSI" r:id="rId22" sheetId="20"/>
-    <sheet name="RESPON" r:id="rId23" sheetId="21"/>
+    <sheet name="HEADER" sheetId="1" r:id="rId1"/>
+    <sheet name="ENTITAS" sheetId="2" r:id="rId2"/>
+    <sheet name="DOKUMEN" sheetId="3" r:id="rId3"/>
+    <sheet name="PENGANGKUT" sheetId="4" r:id="rId4"/>
+    <sheet name="KEMASAN" sheetId="5" r:id="rId5"/>
+    <sheet name="KONTAINER" sheetId="6" r:id="rId6"/>
+    <sheet name="KOMPONENBIAYA" sheetId="7" r:id="rId7"/>
+    <sheet name="BARANG" sheetId="8" r:id="rId8"/>
+    <sheet name="BARANGTARIF" sheetId="9" r:id="rId9"/>
+    <sheet name="BARANGDOKUMEN" sheetId="10" r:id="rId10"/>
+    <sheet name="BARANGENTITAS" sheetId="11" r:id="rId11"/>
+    <sheet name="BARANGSPEKKHUSUS" sheetId="12" r:id="rId12"/>
+    <sheet name="BARANGVD" sheetId="13" r:id="rId13"/>
+    <sheet name="BAHANBAKU" sheetId="14" r:id="rId14"/>
+    <sheet name="BAHANBAKUTARIF" sheetId="15" r:id="rId15"/>
+    <sheet name="BAHANBAKUDOKUMEN" sheetId="16" r:id="rId16"/>
+    <sheet name="PUNGUTAN" sheetId="17" r:id="rId17"/>
+    <sheet name="JAMINAN" sheetId="18" r:id="rId18"/>
+    <sheet name="BANKDEVISA" sheetId="19" r:id="rId19"/>
+    <sheet name="VERSI" sheetId="20" r:id="rId20"/>
+    <sheet name="RESPON" sheetId="21" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1367,19 +1388,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd-MM-yyyy HH:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11.00"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="12.00"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
@@ -1406,123 +1427,418 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:DC6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="25.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="25.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="48" max="48" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="49" max="49" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="50" max="50" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="51" max="51" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="52" max="52" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="53" max="53" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="54" max="54" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="55" max="55" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="56" max="56" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="57" max="57" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="58" max="58" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="60" max="60" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="61" max="61" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="62" max="62" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="63" max="63" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="64" max="64" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="65" max="65" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="66" max="66" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="67" max="67" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="70" max="70" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="71" max="71" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="73" max="73" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="74" max="74" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="76" max="76" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="77" max="77" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="78" max="78" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="79" max="79" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="83" max="83" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="84" max="84" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="85" max="85" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="86" max="86" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="87" max="87" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="88" max="88" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="89" max="89" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="90" max="90" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="91" max="91" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="92" max="92" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="93" max="93" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="94" max="94" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="95" max="95" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="96" max="96" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="97" max="97" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="98" max="98" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="99" max="99" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="100" max="100" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="101" max="101" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="102" max="102" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="103" max="103" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="104" max="104" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="105" max="105" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="106" max="106" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="107" max="107" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="51" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="60" max="61" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="92" max="93" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="106" max="107" width="24.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:107" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1845,7 +2161,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
@@ -1867,53 +2183,53 @@
       <c r="O2" t="s">
         <v>108</v>
       </c>
-      <c r="BK2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>7413774.2</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>7413774.2</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB2" t="n">
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>0</v>
+      </c>
+      <c r="BO2">
+        <v>0</v>
+      </c>
+      <c r="BP2">
+        <v>0</v>
+      </c>
+      <c r="BQ2">
+        <v>0</v>
+      </c>
+      <c r="BR2">
+        <v>0</v>
+      </c>
+      <c r="BS2">
+        <v>0</v>
+      </c>
+      <c r="BT2">
+        <v>0</v>
+      </c>
+      <c r="BU2">
+        <v>0</v>
+      </c>
+      <c r="BV2">
+        <v>7413774.2000000002</v>
+      </c>
+      <c r="BW2">
+        <v>1</v>
+      </c>
+      <c r="BY2">
+        <v>7413774.2000000002</v>
+      </c>
+      <c r="CA2">
+        <v>0</v>
+      </c>
+      <c r="CB2">
         <v>69.75</v>
       </c>
-      <c r="CC2" t="n">
+      <c r="CC2">
         <v>68.2</v>
       </c>
-      <c r="CD2" t="n">
-        <v>0.0</v>
+      <c r="CD2">
+        <v>0</v>
       </c>
       <c r="CE2" t="s">
         <v>110</v>
@@ -1936,17 +2252,17 @@
       <c r="CQ2" t="s">
         <v>111</v>
       </c>
-      <c r="CT2" t="n">
+      <c r="CT2">
         <v>815515.16</v>
       </c>
-      <c r="CU2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="CU2">
+        <v>0</v>
+      </c>
+      <c r="CV2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>116</v>
       </c>
@@ -1968,53 +2284,53 @@
       <c r="O3" t="s">
         <v>108</v>
       </c>
-      <c r="BK3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU3" t="n">
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
         <v>2247.34</v>
       </c>
-      <c r="BV3" t="n">
-        <v>3.92722665E7</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>17475.0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>3.92722665E7</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB3" t="n">
+      <c r="BV3">
+        <v>39272266.5</v>
+      </c>
+      <c r="BW3">
+        <v>17475</v>
+      </c>
+      <c r="BY3">
+        <v>39272266.5</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3">
         <v>208.95</v>
       </c>
-      <c r="CC3" t="n">
+      <c r="CC3">
         <v>179.35</v>
       </c>
-      <c r="CD3" t="n">
-        <v>0.0</v>
+      <c r="CD3">
+        <v>0</v>
       </c>
       <c r="CE3" t="s">
         <v>110</v>
@@ -2037,17 +2353,17 @@
       <c r="CQ3" t="s">
         <v>111</v>
       </c>
-      <c r="CT3" t="n">
+      <c r="CT3">
         <v>4319949.32</v>
       </c>
-      <c r="CU3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="CU3">
+        <v>0</v>
+      </c>
+      <c r="CV3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>120</v>
       </c>
@@ -2069,53 +2385,53 @@
       <c r="O4" t="s">
         <v>108</v>
       </c>
-      <c r="BK4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>17475.0</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB4" t="n">
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>17475</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4">
         <v>1981.57</v>
       </c>
-      <c r="CC4" t="n">
+      <c r="CC4">
         <v>1981.57</v>
       </c>
-      <c r="CD4" t="n">
-        <v>0.0</v>
+      <c r="CD4">
+        <v>0</v>
       </c>
       <c r="CE4" t="s">
         <v>110</v>
@@ -2138,17 +2454,17 @@
       <c r="CQ4" t="s">
         <v>111</v>
       </c>
-      <c r="CT4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CU4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV4" t="n">
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="CT4">
+        <v>0</v>
+      </c>
+      <c r="CU4">
+        <v>0</v>
+      </c>
+      <c r="CV4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>122</v>
       </c>
@@ -2170,53 +2486,53 @@
       <c r="O5" t="s">
         <v>108</v>
       </c>
-      <c r="BK5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU5" t="n">
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
         <v>38490.85</v>
       </c>
-      <c r="BV5" t="n">
-        <v>6.7262760375E8</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>17475.0</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>6.7262760375E8</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB5" t="n">
+      <c r="BV5">
+        <v>672627603.75</v>
+      </c>
+      <c r="BW5">
+        <v>17475</v>
+      </c>
+      <c r="BY5">
+        <v>672627603.75</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5">
         <v>4275.93</v>
       </c>
-      <c r="CC5" t="n">
+      <c r="CC5">
         <v>3788.04</v>
       </c>
-      <c r="CD5" t="n">
-        <v>0.0</v>
+      <c r="CD5">
+        <v>0</v>
       </c>
       <c r="CE5" t="s">
         <v>110</v>
@@ -2239,17 +2555,17 @@
       <c r="CQ5" t="s">
         <v>111</v>
       </c>
-      <c r="CT5" t="n">
-        <v>7.398903641E7</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="CT5">
+        <v>73989036.409999996</v>
+      </c>
+      <c r="CU5">
+        <v>0</v>
+      </c>
+      <c r="CV5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -2271,53 +2587,53 @@
       <c r="O6" t="s">
         <v>108</v>
       </c>
-      <c r="BK6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU6" t="n">
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
         <v>10749.2</v>
       </c>
-      <c r="BV6" t="n">
-        <v>1.8784227E8</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>17475.0</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>1.8784227E8</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB6" t="n">
+      <c r="BV6">
+        <v>187842270</v>
+      </c>
+      <c r="BW6">
+        <v>17475</v>
+      </c>
+      <c r="BY6">
+        <v>187842270</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6">
         <v>3994.22</v>
       </c>
-      <c r="CC6" t="n">
+      <c r="CC6">
         <v>3572.33</v>
       </c>
-      <c r="CD6" t="n">
-        <v>0.0</v>
+      <c r="CD6">
+        <v>0</v>
       </c>
       <c r="CE6" t="s">
         <v>110</v>
@@ -2340,41 +2656,37 @@
       <c r="CQ6" t="s">
         <v>111</v>
       </c>
-      <c r="CT6" t="n">
-        <v>2.06626497E7</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>11.0</v>
+      <c r="CT6">
+        <v>20662649.699999999</v>
+      </c>
+      <c r="CU6">
+        <v>0</v>
+      </c>
+      <c r="CV6">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2389,29 +2701,25 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2423,28 +2731,24 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2459,32 +2763,28 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2508,60 +2808,55 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:AO20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="69.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="69.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2686,14 +2981,14 @@
         <v>299</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>2</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
@@ -2723,8 +3018,8 @@
       <c r="L2" t="s">
         <v>309</v>
       </c>
-      <c r="M2" t="n">
-        <v>143.0</v>
+      <c r="M2">
+        <v>143</v>
       </c>
       <c r="P2" t="s">
         <v>105</v>
@@ -2741,42 +3036,42 @@
       <c r="T2" t="s">
         <v>350</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U2">
         <v>3</v>
       </c>
-      <c r="V2" t="n">
+      <c r="V2">
         <v>61.2</v>
       </c>
-      <c r="Y2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2037750.0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>2037750</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>104</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>3</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
@@ -2806,8 +3101,8 @@
       <c r="L3" t="s">
         <v>305</v>
       </c>
-      <c r="M3" t="n">
-        <v>11004.0</v>
+      <c r="M3">
+        <v>11004</v>
       </c>
       <c r="P3" t="s">
         <v>105</v>
@@ -2824,42 +3119,42 @@
       <c r="T3" t="s">
         <v>350</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U3">
         <v>1</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V3">
         <v>22.5</v>
       </c>
-      <c r="Y3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
         <v>3367774.2</v>
       </c>
-      <c r="AC3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
@@ -2889,8 +3184,8 @@
       <c r="L4" t="s">
         <v>309</v>
       </c>
-      <c r="M4" t="n">
-        <v>277.0</v>
+      <c r="M4">
+        <v>277</v>
       </c>
       <c r="P4" t="s">
         <v>105</v>
@@ -2907,42 +3202,42 @@
       <c r="T4" t="s">
         <v>350</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U4">
         <v>2</v>
       </c>
-      <c r="V4" t="n">
+      <c r="V4">
         <v>89.6</v>
       </c>
-      <c r="Y4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2008250.0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>2008250</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>116</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
@@ -2972,7 +3267,7 @@
       <c r="L5" t="s">
         <v>319</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>39.78</v>
       </c>
       <c r="P5" t="s">
@@ -2990,42 +3285,42 @@
       <c r="T5" t="s">
         <v>361</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U5">
         <v>1</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V5">
         <v>8715.41</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Y5">
         <v>194.13</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="Z5">
         <v>3392421.75</v>
       </c>
-      <c r="AA5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
         <v>3392421.75</v>
       </c>
-      <c r="AC5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>116</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>2</v>
       </c>
       <c r="D6" t="s">
@@ -3055,7 +3350,7 @@
       <c r="L6" t="s">
         <v>319</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>4.42</v>
       </c>
       <c r="P6" t="s">
@@ -3073,42 +3368,42 @@
       <c r="T6" t="s">
         <v>367</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U6">
         <v>1</v>
       </c>
-      <c r="V6" t="n">
+      <c r="V6">
         <v>3863.7</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Y6">
         <v>21.04</v>
       </c>
-      <c r="Z6" t="n">
-        <v>367674.0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="Z6">
+        <v>367674</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>116</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
@@ -3138,7 +3433,7 @@
       <c r="L7" t="s">
         <v>319</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>121.63</v>
       </c>
       <c r="P7" t="s">
@@ -3156,42 +3451,42 @@
       <c r="T7" t="s">
         <v>361</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U7">
         <v>1</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V7">
         <v>8715.41</v>
       </c>
-      <c r="Y7" t="n">
-        <v>593.55</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.037228625E7</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.037228625E7</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="Y7">
+        <v>593.54999999999995</v>
+      </c>
+      <c r="Z7">
+        <v>10372286.25</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>10372286.25</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>116</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>2</v>
       </c>
       <c r="D8" t="s">
@@ -3221,7 +3516,7 @@
       <c r="L8" t="s">
         <v>319</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>13.52</v>
       </c>
       <c r="P8" t="s">
@@ -3239,42 +3534,42 @@
       <c r="T8" t="s">
         <v>367</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U8">
         <v>1</v>
       </c>
-      <c r="V8" t="n">
+      <c r="V8">
         <v>3863.7</v>
       </c>
-      <c r="Y8" t="n">
-        <v>64.35</v>
-      </c>
-      <c r="Z8" t="n">
+      <c r="Y8">
+        <v>64.349999999999994</v>
+      </c>
+      <c r="Z8">
         <v>1124516.25</v>
       </c>
-      <c r="AA8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>120</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
@@ -3304,7 +3599,7 @@
       <c r="L9" t="s">
         <v>319</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>1981.57</v>
       </c>
       <c r="P9" t="s">
@@ -3322,42 +3617,42 @@
       <c r="T9" t="s">
         <v>372</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U9">
         <v>1</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V9">
         <v>6271.7</v>
       </c>
-      <c r="Y9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>6.1088633445E8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>610886334.45000005</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>122</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
@@ -3387,7 +3682,7 @@
       <c r="L10" t="s">
         <v>319</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>3428.18</v>
       </c>
       <c r="P10" t="s">
@@ -3405,42 +3700,42 @@
       <c r="T10" t="s">
         <v>374</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U10">
         <v>1</v>
       </c>
-      <c r="V10" t="n">
+      <c r="V10">
         <v>7052.98</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Y10">
         <v>16729.52</v>
       </c>
-      <c r="Z10" t="n">
-        <v>2.92348362E8</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.92348362E8</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="Z10">
+        <v>292348362</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>292348362</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>122</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>2</v>
       </c>
       <c r="D11" t="s">
@@ -3470,7 +3765,7 @@
       <c r="L11" t="s">
         <v>319</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>359.86</v>
       </c>
       <c r="P11" t="s">
@@ -3488,42 +3783,42 @@
       <c r="T11" t="s">
         <v>379</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U11">
         <v>1</v>
       </c>
-      <c r="V11" t="n">
+      <c r="V11">
         <v>1032.5</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Y11">
         <v>3688.57</v>
       </c>
-      <c r="Z11" t="n">
-        <v>6.445776075E7</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="Z11">
+        <v>64457760.75</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>124</v>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
         <v>5</v>
       </c>
       <c r="D12" t="s">
@@ -3553,7 +3848,7 @@
       <c r="L12" t="s">
         <v>324</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>6398.85</v>
       </c>
       <c r="P12" t="s">
@@ -3571,42 +3866,42 @@
       <c r="T12" t="s">
         <v>384</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
         <v>26.7</v>
       </c>
-      <c r="Y12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
         <v>5403.19</v>
       </c>
-      <c r="AC12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>124</v>
       </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
         <v>4</v>
       </c>
       <c r="D13" t="s">
@@ -3636,8 +3931,8 @@
       <c r="L13" t="s">
         <v>305</v>
       </c>
-      <c r="M13" t="n">
-        <v>15356.0</v>
+      <c r="M13">
+        <v>15356</v>
       </c>
       <c r="P13" t="s">
         <v>105</v>
@@ -3654,42 +3949,42 @@
       <c r="T13" t="s">
         <v>384</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>154.55</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>6266322.92</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>154.55000000000001</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>6266322.9199999999</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>124</v>
       </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
         <v>3</v>
       </c>
       <c r="D14" t="s">
@@ -3719,7 +4014,7 @@
       <c r="L14" t="s">
         <v>309</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>199.63</v>
       </c>
       <c r="P14" t="s">
@@ -3737,42 +4032,42 @@
       <c r="T14" t="s">
         <v>384</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
         <v>108.72</v>
       </c>
-      <c r="Y14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
         <v>2844727.5</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AC14">
         <v>199.63</v>
       </c>
-      <c r="AD14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>124</v>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
         <v>4</v>
       </c>
       <c r="D15" t="s">
@@ -3802,8 +4097,8 @@
       <c r="L15" t="s">
         <v>305</v>
       </c>
-      <c r="M15" t="n">
-        <v>861.0</v>
+      <c r="M15">
+        <v>861</v>
       </c>
       <c r="P15" t="s">
         <v>105</v>
@@ -3820,42 +4115,42 @@
       <c r="T15" t="s">
         <v>392</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
         <v>2797.1</v>
       </c>
-      <c r="Y15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>9828961.63</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>9828961.6300000008</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>124</v>
       </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
         <v>2</v>
       </c>
       <c r="D16" t="s">
@@ -3885,8 +4180,8 @@
       <c r="L16" t="s">
         <v>319</v>
       </c>
-      <c r="M16" t="n">
-        <v>3839.0</v>
+      <c r="M16">
+        <v>3839</v>
       </c>
       <c r="P16" t="s">
         <v>105</v>
@@ -3903,42 +4198,42 @@
       <c r="T16" t="s">
         <v>396</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
         <v>10532.71</v>
       </c>
-      <c r="Y16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>4.3584811921E8</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>435848119.20999998</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>124</v>
       </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
@@ -3968,8 +4263,8 @@
       <c r="L17" t="s">
         <v>305</v>
       </c>
-      <c r="M17" t="n">
-        <v>15356.0</v>
+      <c r="M17">
+        <v>15356</v>
       </c>
       <c r="P17" t="s">
         <v>105</v>
@@ -3986,42 +4281,42 @@
       <c r="T17" t="s">
         <v>384</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>78.9</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.74396364E8</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>274396364</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>124</v>
       </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
         <v>2</v>
       </c>
       <c r="D18" t="s">
@@ -4051,7 +4346,7 @@
       <c r="L18" t="s">
         <v>309</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18">
         <v>386.97</v>
       </c>
       <c r="P18" t="s">
@@ -4069,42 +4364,42 @@
       <c r="T18" t="s">
         <v>398</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
         <v>167.61</v>
       </c>
-      <c r="Y18" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
         <v>2805532.5</v>
       </c>
-      <c r="AC18" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>124</v>
       </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
         <v>3</v>
       </c>
       <c r="D19" t="s">
@@ -4134,8 +4429,8 @@
       <c r="L19" t="s">
         <v>319</v>
       </c>
-      <c r="M19" t="n">
-        <v>261.052</v>
+      <c r="M19">
+        <v>261.05200000000002</v>
       </c>
       <c r="P19" t="s">
         <v>105</v>
@@ -4152,42 +4447,42 @@
       <c r="T19" t="s">
         <v>384</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
         <v>473.36</v>
       </c>
-      <c r="Y19" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>4537099.73</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>4537099.7300000004</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>124</v>
       </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
@@ -4217,8 +4512,8 @@
       <c r="L20" t="s">
         <v>243</v>
       </c>
-      <c r="M20" t="n">
-        <v>35.0</v>
+      <c r="M20">
+        <v>35</v>
       </c>
       <c r="P20" t="s">
         <v>105</v>
@@ -4235,79 +4530,75 @@
       <c r="T20" t="s">
         <v>392</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
         <v>67.75</v>
       </c>
-      <c r="Y20" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
         <v>125.125</v>
       </c>
-      <c r="AC20" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE20" t="n">
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:Y12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4384,14 +4675,14 @@
         <v>239</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>116</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>2</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>2</v>
       </c>
       <c r="D2" t="s">
@@ -4403,39 +4694,39 @@
       <c r="F2" t="s">
         <v>109</v>
       </c>
-      <c r="G2" t="n">
-        <v>7500.0</v>
+      <c r="G2">
+        <v>7500</v>
       </c>
       <c r="H2" t="s">
         <v>130</v>
       </c>
-      <c r="I2" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>33150.0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.0</v>
+      <c r="I2">
+        <v>100</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>33150</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
       </c>
       <c r="M2" t="s">
         <v>319</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>4.42</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>116</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
@@ -4447,39 +4738,39 @@
       <c r="F3" t="s">
         <v>108</v>
       </c>
-      <c r="G3" t="n">
-        <v>11.0</v>
+      <c r="G3">
+        <v>11</v>
       </c>
       <c r="H3" t="s">
         <v>132</v>
       </c>
-      <c r="I3" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="I3">
+        <v>100</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
         <v>47123.95</v>
       </c>
-      <c r="L3" t="n">
-        <v>0.0</v>
+      <c r="L3">
+        <v>0</v>
       </c>
       <c r="M3" t="s">
         <v>319</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>4.42</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>116</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>2</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
@@ -4491,39 +4782,39 @@
       <c r="F4" t="s">
         <v>108</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>7.5</v>
       </c>
       <c r="H4" t="s">
         <v>130</v>
       </c>
-      <c r="I4" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>27575.55</v>
       </c>
-      <c r="L4" t="n">
-        <v>0.0</v>
+      <c r="L4">
+        <v>0</v>
       </c>
       <c r="M4" t="s">
         <v>319</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>4.42</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>116</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="s">
@@ -4535,39 +4826,39 @@
       <c r="F5" t="s">
         <v>108</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>2.5</v>
       </c>
       <c r="H5" t="s">
         <v>132</v>
       </c>
-      <c r="I5" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <v>10709.99</v>
       </c>
-      <c r="L5" t="n">
-        <v>0.0</v>
+      <c r="L5">
+        <v>0</v>
       </c>
       <c r="M5" t="s">
         <v>319</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>4.42</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>116</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>2</v>
       </c>
       <c r="D6" t="s">
@@ -4579,39 +4870,39 @@
       <c r="F6" t="s">
         <v>108</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>2.5</v>
       </c>
       <c r="H6" t="s">
         <v>132</v>
       </c>
-      <c r="I6" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>32756.37</v>
       </c>
-      <c r="L6" t="n">
-        <v>0.0</v>
+      <c r="L6">
+        <v>0</v>
       </c>
       <c r="M6" t="s">
         <v>319</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>13.52</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>116</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="s">
@@ -4623,39 +4914,39 @@
       <c r="F7" t="s">
         <v>109</v>
       </c>
-      <c r="G7" t="n">
-        <v>7500.0</v>
+      <c r="G7">
+        <v>7500</v>
       </c>
       <c r="H7" t="s">
         <v>130</v>
       </c>
-      <c r="I7" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>101400.0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.0</v>
+      <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>101400</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
       </c>
       <c r="M7" t="s">
         <v>319</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>13.52</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>116</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>2</v>
       </c>
       <c r="D8" t="s">
@@ -4667,39 +4958,39 @@
       <c r="F8" t="s">
         <v>108</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>7.5</v>
       </c>
       <c r="H8" t="s">
         <v>130</v>
       </c>
-      <c r="I8" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>84338.72</v>
       </c>
-      <c r="L8" t="n">
-        <v>0.0</v>
+      <c r="L8">
+        <v>0</v>
       </c>
       <c r="M8" t="s">
         <v>319</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>13.52</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>116</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" t="s">
@@ -4711,39 +5002,39 @@
       <c r="F9" t="s">
         <v>108</v>
       </c>
-      <c r="G9" t="n">
-        <v>11.0</v>
+      <c r="G9">
+        <v>11</v>
       </c>
       <c r="H9" t="s">
         <v>132</v>
       </c>
-      <c r="I9" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>144128.05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.0</v>
+      <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>144128.04999999999</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
       </c>
       <c r="M9" t="s">
         <v>319</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>13.52</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>122</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>2</v>
       </c>
       <c r="D10" t="s">
@@ -4755,39 +5046,39 @@
       <c r="F10" t="s">
         <v>108</v>
       </c>
-      <c r="G10" t="n">
-        <v>5.0</v>
+      <c r="G10">
+        <v>5</v>
       </c>
       <c r="H10" t="s">
         <v>130</v>
       </c>
-      <c r="I10" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="I10">
+        <v>100</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>3222888.04</v>
       </c>
-      <c r="L10" t="n">
-        <v>0.0</v>
+      <c r="L10">
+        <v>0</v>
       </c>
       <c r="M10" t="s">
         <v>319</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>359.86</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>122</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>2</v>
       </c>
       <c r="D11" t="s">
@@ -4799,39 +5090,39 @@
       <c r="F11" t="s">
         <v>108</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>2.5</v>
       </c>
       <c r="H11" t="s">
         <v>132</v>
       </c>
-      <c r="I11" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="I11">
+        <v>100</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>1692016.22</v>
       </c>
-      <c r="L11" t="n">
-        <v>0.0</v>
+      <c r="L11">
+        <v>0</v>
       </c>
       <c r="M11" t="s">
         <v>319</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11">
         <v>359.86</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>122</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>2</v>
       </c>
       <c r="D12" t="s">
@@ -4843,58 +5134,54 @@
       <c r="F12" t="s">
         <v>108</v>
       </c>
-      <c r="G12" t="n">
-        <v>11.0</v>
+      <c r="G12">
+        <v>11</v>
       </c>
       <c r="H12" t="s">
         <v>132</v>
       </c>
-      <c r="I12" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>7444871.37</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.0</v>
+      <c r="I12">
+        <v>100</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>7444871.3700000001</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
       </c>
       <c r="M12" t="s">
         <v>319</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12">
         <v>359.86</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4915,31 +5202,27 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4956,7 +5239,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>116</v>
       </c>
@@ -4966,11 +5249,11 @@
       <c r="C2" t="s">
         <v>131</v>
       </c>
-      <c r="D2" t="n">
-        <v>112000.0</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="D2">
+        <v>112000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>116</v>
       </c>
@@ -4980,11 +5263,11 @@
       <c r="C3" t="s">
         <v>133</v>
       </c>
-      <c r="D3" t="n">
-        <v>44000.0</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="D3">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>116</v>
       </c>
@@ -4994,11 +5277,11 @@
       <c r="C4" t="s">
         <v>134</v>
       </c>
-      <c r="D4" t="n">
-        <v>135000.0</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="D4">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>116</v>
       </c>
@@ -5008,11 +5291,11 @@
       <c r="C5" t="s">
         <v>135</v>
       </c>
-      <c r="D5" t="n">
-        <v>192000.0</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="D5">
+        <v>192000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>122</v>
       </c>
@@ -5022,11 +5305,11 @@
       <c r="C6" t="s">
         <v>131</v>
       </c>
-      <c r="D6" t="n">
-        <v>3223000.0</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="D6">
+        <v>3223000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>122</v>
       </c>
@@ -5036,11 +5319,11 @@
       <c r="C7" t="s">
         <v>135</v>
       </c>
-      <c r="D7" t="n">
-        <v>7445000.0</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="D7">
+        <v>7445000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>122</v>
       </c>
@@ -5050,41 +5333,37 @@
       <c r="C8" t="s">
         <v>133</v>
       </c>
-      <c r="D8" t="n">
-        <v>1693000.0</v>
+      <c r="D8">
+        <v>1693000</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5117,27 +5396,23 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5152,41 +5427,37 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:P16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="31.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="107.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="25.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="107.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5236,7 +5507,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
@@ -5271,7 +5542,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -5300,7 +5571,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
@@ -5338,7 +5609,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>116</v>
       </c>
@@ -5367,7 +5638,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>116</v>
       </c>
@@ -5396,7 +5667,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>116</v>
       </c>
@@ -5434,7 +5705,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>120</v>
       </c>
@@ -5472,7 +5743,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>120</v>
       </c>
@@ -5507,7 +5778,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>120</v>
       </c>
@@ -5530,7 +5801,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>122</v>
       </c>
@@ -5568,7 +5839,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>122</v>
       </c>
@@ -5603,7 +5874,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>122</v>
       </c>
@@ -5632,7 +5903,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>124</v>
       </c>
@@ -5670,7 +5941,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>124</v>
       </c>
@@ -5705,7 +5976,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>124</v>
       </c>
@@ -5735,58 +6006,50 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>432</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5800,7 +6063,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>116</v>
       </c>
@@ -5814,7 +6077,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>122</v>
       </c>
@@ -5828,7 +6091,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>122</v>
       </c>
@@ -5839,7 +6102,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>122</v>
       </c>
@@ -5850,7 +6113,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -5864,7 +6127,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>104</v>
       </c>
@@ -5878,7 +6141,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>120</v>
       </c>
@@ -5893,32 +6156,28 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5941,12 +6200,12 @@
         <v>188</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
-        <v>1.0</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>189</v>
@@ -5958,12 +6217,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>104</v>
       </c>
-      <c r="B3" t="n">
-        <v>2.0</v>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>191</v>
@@ -5975,12 +6234,12 @@
         <v>193</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
-      <c r="B4" t="n">
-        <v>3.0</v>
+      <c r="B4">
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>105</v>
@@ -5992,12 +6251,12 @@
         <v>195</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>116</v>
       </c>
-      <c r="B5" t="n">
-        <v>1.0</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="C5" t="s">
         <v>196</v>
@@ -6009,12 +6268,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>116</v>
       </c>
-      <c r="B6" t="n">
-        <v>2.0</v>
+      <c r="B6">
+        <v>2</v>
       </c>
       <c r="C6" t="s">
         <v>196</v>
@@ -6026,12 +6285,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>116</v>
       </c>
-      <c r="B7" t="n">
-        <v>3.0</v>
+      <c r="B7">
+        <v>3</v>
       </c>
       <c r="C7" t="s">
         <v>189</v>
@@ -6043,12 +6302,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>116</v>
       </c>
-      <c r="B8" t="n">
-        <v>4.0</v>
+      <c r="B8">
+        <v>4</v>
       </c>
       <c r="C8" t="s">
         <v>189</v>
@@ -6060,12 +6319,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>116</v>
       </c>
-      <c r="B9" t="n">
-        <v>5.0</v>
+      <c r="B9">
+        <v>5</v>
       </c>
       <c r="C9" t="s">
         <v>201</v>
@@ -6077,12 +6336,12 @@
         <v>203</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>116</v>
       </c>
-      <c r="B10" t="n">
-        <v>6.0</v>
+      <c r="B10">
+        <v>6</v>
       </c>
       <c r="C10" t="s">
         <v>105</v>
@@ -6094,12 +6353,12 @@
         <v>205</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>116</v>
       </c>
-      <c r="B11" t="n">
-        <v>7.0</v>
+      <c r="B11">
+        <v>7</v>
       </c>
       <c r="C11" t="s">
         <v>206</v>
@@ -6111,12 +6370,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>120</v>
       </c>
-      <c r="B12" t="n">
-        <v>1.0</v>
+      <c r="B12">
+        <v>1</v>
       </c>
       <c r="C12" t="s">
         <v>189</v>
@@ -6128,12 +6387,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>120</v>
       </c>
-      <c r="B13" t="n">
-        <v>2.0</v>
+      <c r="B13">
+        <v>2</v>
       </c>
       <c r="C13" t="s">
         <v>105</v>
@@ -6145,12 +6404,12 @@
         <v>210</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>120</v>
       </c>
-      <c r="B14" t="n">
-        <v>3.0</v>
+      <c r="B14">
+        <v>3</v>
       </c>
       <c r="C14" t="s">
         <v>191</v>
@@ -6162,12 +6421,12 @@
         <v>212</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>122</v>
       </c>
-      <c r="B15" t="n">
-        <v>1.0</v>
+      <c r="B15">
+        <v>1</v>
       </c>
       <c r="C15" t="s">
         <v>196</v>
@@ -6179,12 +6438,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>122</v>
       </c>
-      <c r="B16" t="n">
-        <v>2.0</v>
+      <c r="B16">
+        <v>2</v>
       </c>
       <c r="C16" t="s">
         <v>206</v>
@@ -6196,12 +6455,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>122</v>
       </c>
-      <c r="B17" t="n">
-        <v>3.0</v>
+      <c r="B17">
+        <v>3</v>
       </c>
       <c r="C17" t="s">
         <v>189</v>
@@ -6213,12 +6472,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>122</v>
       </c>
-      <c r="B18" t="n">
-        <v>4.0</v>
+      <c r="B18">
+        <v>4</v>
       </c>
       <c r="C18" t="s">
         <v>105</v>
@@ -6230,12 +6489,12 @@
         <v>216</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>122</v>
       </c>
-      <c r="B19" t="n">
-        <v>5.0</v>
+      <c r="B19">
+        <v>5</v>
       </c>
       <c r="C19" t="s">
         <v>201</v>
@@ -6247,12 +6506,12 @@
         <v>218</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>124</v>
       </c>
-      <c r="B20" t="n">
-        <v>1.0</v>
+      <c r="B20">
+        <v>1</v>
       </c>
       <c r="C20" t="s">
         <v>196</v>
@@ -6264,12 +6523,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>124</v>
       </c>
-      <c r="B21" t="n">
-        <v>2.0</v>
+      <c r="B21">
+        <v>2</v>
       </c>
       <c r="C21" t="s">
         <v>191</v>
@@ -6281,12 +6540,12 @@
         <v>193</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>124</v>
       </c>
-      <c r="B22" t="n">
-        <v>3.0</v>
+      <c r="B22">
+        <v>3</v>
       </c>
       <c r="C22" t="s">
         <v>105</v>
@@ -6298,12 +6557,12 @@
         <v>221</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>124</v>
       </c>
-      <c r="B23" t="n">
-        <v>4.0</v>
+      <c r="B23">
+        <v>4</v>
       </c>
       <c r="C23" t="s">
         <v>105</v>
@@ -6315,12 +6574,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>124</v>
       </c>
-      <c r="B24" t="n">
-        <v>5.0</v>
+      <c r="B24">
+        <v>5</v>
       </c>
       <c r="C24" t="s">
         <v>105</v>
@@ -6332,12 +6591,12 @@
         <v>225</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>124</v>
       </c>
-      <c r="B25" t="n">
-        <v>6.0</v>
+      <c r="B25">
+        <v>6</v>
       </c>
       <c r="C25" t="s">
         <v>105</v>
@@ -6349,12 +6608,12 @@
         <v>195</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>124</v>
       </c>
-      <c r="B26" t="n">
-        <v>7.0</v>
+      <c r="B26">
+        <v>7</v>
       </c>
       <c r="C26" t="s">
         <v>105</v>
@@ -6366,12 +6625,12 @@
         <v>227</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>124</v>
       </c>
-      <c r="B27" t="n">
-        <v>8.0</v>
+      <c r="B27">
+        <v>8</v>
       </c>
       <c r="C27" t="s">
         <v>189</v>
@@ -6383,12 +6642,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>124</v>
       </c>
-      <c r="B28" t="n">
-        <v>9.0</v>
+      <c r="B28">
+        <v>9</v>
       </c>
       <c r="C28" t="s">
         <v>189</v>
@@ -6401,34 +6660,30 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6457,11 +6712,11 @@
         <v>236</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
@@ -6471,11 +6726,11 @@
         <v>207</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>116</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
@@ -6485,11 +6740,11 @@
         <v>207</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>120</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
@@ -6499,11 +6754,11 @@
         <v>207</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>122</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
@@ -6513,11 +6768,11 @@
         <v>207</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>124</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
@@ -6528,30 +6783,26 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6571,103 +6822,99 @@
         <v>241</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>242</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>116</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>243</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>8</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>120</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
         <v>244</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>103</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>122</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
         <v>245</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>165</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>124</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>242</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>861</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6691,40 +6938,34 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:T1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6787,87 +7028,76 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:BR9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="57.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="48" max="48" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="49" max="49" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="50" max="50" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="51" max="51" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="52" max="52" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="53" max="53" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="54" max="54" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="55" max="55" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="56" max="56" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="57" max="57" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="58" max="58" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="59" max="59" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="60" max="60" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="61" max="61" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="62" max="62" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="63" max="63" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="64" max="64" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="65" max="65" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="66" max="66" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="67" max="67" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="68" max="68" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="69" max="69" width="30.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="70" max="70" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="57.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="47" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="51" max="52" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="63" max="64" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:70" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7079,11 +7309,11 @@
         <v>302</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>104</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>3</v>
       </c>
       <c r="C2" t="s">
@@ -7110,57 +7340,57 @@
       <c r="J2" t="s">
         <v>305</v>
       </c>
-      <c r="K2" t="n">
-        <v>11004.0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="K2">
+        <v>11004</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="Z2">
         <v>3367774.2</v>
       </c>
-      <c r="AI2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.0</v>
+      <c r="AA2">
+        <v>3367774.2</v>
+      </c>
+      <c r="AB2">
+        <v>1</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>3367774.2</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
       </c>
       <c r="BR2" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>104</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
@@ -7187,60 +7417,60 @@
       <c r="J3" t="s">
         <v>309</v>
       </c>
-      <c r="K3" t="n">
-        <v>143.0</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="K3">
+        <v>143</v>
+      </c>
+      <c r="T3">
         <v>22.88</v>
       </c>
-      <c r="V3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>2037750.0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.0</v>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>2037750</v>
+      </c>
+      <c r="AA3">
+        <v>2037750</v>
+      </c>
+      <c r="AB3">
+        <v>1</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>2037750</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
       </c>
       <c r="BR3" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
@@ -7267,60 +7497,60 @@
       <c r="J4" t="s">
         <v>309</v>
       </c>
-      <c r="K4" t="n">
-        <v>277.0</v>
-      </c>
-      <c r="T4" t="n">
+      <c r="K4">
+        <v>277</v>
+      </c>
+      <c r="T4">
         <v>44.32</v>
       </c>
-      <c r="V4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2008250.0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.0</v>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>2008250</v>
+      </c>
+      <c r="AA4">
+        <v>2008250</v>
+      </c>
+      <c r="AB4">
+        <v>1</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>2008250</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
       </c>
       <c r="BR4" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>116</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
@@ -7347,63 +7577,63 @@
       <c r="J5" t="s">
         <v>315</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>134.19</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T5">
         <v>44.2</v>
       </c>
-      <c r="V5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
         <v>563.6</v>
       </c>
-      <c r="AA5" t="n">
-        <v>9848910.0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>17475.0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>9848910.0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0.0</v>
+      <c r="AA5">
+        <v>9848910</v>
+      </c>
+      <c r="AB5">
+        <v>17475</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>9848910</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
       </c>
       <c r="AW5" t="s">
         <v>108</v>
       </c>
-      <c r="BJ5" t="n">
-        <v>0.0</v>
+      <c r="BJ5">
+        <v>0</v>
       </c>
       <c r="BR5" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>116</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
@@ -7430,63 +7660,63 @@
       <c r="J6" t="s">
         <v>315</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>400.89</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T6">
         <v>135.15</v>
       </c>
-      <c r="V6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z6" t="n">
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
         <v>1683.74</v>
       </c>
-      <c r="AA6" t="n">
-        <v>2.94233565E7</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>17475.0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2.94233565E7</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0.0</v>
+      <c r="AA6">
+        <v>29423356.5</v>
+      </c>
+      <c r="AB6">
+        <v>17475</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>29423356.5</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
       </c>
       <c r="AW6" t="s">
         <v>108</v>
       </c>
-      <c r="BJ6" t="n">
-        <v>0.0</v>
+      <c r="BJ6">
+        <v>0</v>
       </c>
       <c r="BR6" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>120</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
@@ -7513,57 +7743,57 @@
       <c r="J7" t="s">
         <v>319</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>1981.57</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T7">
         <v>1981.57</v>
       </c>
-      <c r="Z7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>17475.0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.0</v>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>17475</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
       </c>
       <c r="BR7" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>122</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
@@ -7590,57 +7820,57 @@
       <c r="J8" t="s">
         <v>324</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>13697.81</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T8">
         <v>3788.04</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="Z8">
         <v>38490.85</v>
       </c>
-      <c r="AA8" t="n">
-        <v>6.7262760375E8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>17475.0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>6.7262760375E8</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.0</v>
+      <c r="AA8">
+        <v>672627603.75</v>
+      </c>
+      <c r="AB8">
+        <v>17475</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>672627603.75</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
       </c>
       <c r="BR8" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>124</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
@@ -7667,97 +7897,93 @@
       <c r="J9" t="s">
         <v>305</v>
       </c>
-      <c r="K9" t="n">
-        <v>15356.0</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="K9">
+        <v>15356</v>
+      </c>
+      <c r="T9">
         <v>3572.33</v>
       </c>
-      <c r="V9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z9" t="n">
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
         <v>10749.2</v>
       </c>
-      <c r="AA9" t="n">
-        <v>1.8784227E8</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>17475.0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.8784227E8</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0.0</v>
+      <c r="AA9">
+        <v>187842270</v>
+      </c>
+      <c r="AB9">
+        <v>17475</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>187842270</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
       </c>
       <c r="AW9" t="s">
         <v>108</v>
       </c>
-      <c r="BJ9" t="n">
-        <v>0.0</v>
+      <c r="BJ9">
+        <v>0</v>
       </c>
       <c r="BR9" t="s">
         <v>306</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7817,11 +8043,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>